--- a/data/03_output/evaluaciones/auditoria_manual_8_MultiQuery_Embeddings_CrossEncoder.xlsx
+++ b/data/03_output/evaluaciones/auditoria_manual_8_MultiQuery_Embeddings_CrossEncoder.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Cómo se clasifican los tipos de crédito de la Cartera Crediticia de Consumo no Revolvente para el cálculo de reservas?</t>
+          <t>¿Para consumo no revolvente cómo se define el pago realizado?</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -464,12 +464,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>### Artículo 90.- Las Instituciones al calificar la Cartera Crediticia de Consumo deberán separarla en dos grupos, en razón de si se refiere o no a operaciones de tarjeta de crédito y otros créditos Revolventes, y determinarán a la fecha de la calificación de los créditos las reservas preventivas correspondientes, considerando para tal efecto, la Probabilidad de Incumplimiento, la Severidad de la Pérdida y la Exposición al Incumplimiento de conformidad con lo siguiente:</t>
+          <t>Pago.- Entrega real de la cosa o cantidad debida o la prestación del servicio que se hubiere pactado. No se considerarán como pago el ingreso financiero por devengar proveniente de las operaciones de arrendamiento financiero, factoraje financiero, descuento o cesión de derechos de crédito, ni los intereses que se capitalicen.  
+No se consideran pagos los castigos, quitas, condonaciones, bonificaciones y descuentos que se efectúen a un crédito o grupo de créditos.  
+Pág. 38</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ABCD (B) | A los créditos que sean otorgados a personas físicas y cuyo destino sea la adquisición de bienes de consumo duradero</t>
+          <t>Monto correspondiente a la suma de los pagos realizados por el acreditado en el Periodo de Facturación</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -646,7 +648,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras utilizar las garantías reales financieras para reducir las reservas preventivas según el Artículo 97 Bis 6?</t>
+          <t>¿Qué se consideraría un crédito personal?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -654,12 +656,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>### Artículo 97 Bis 6.- Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas derivadas de la calificación de cartera de los créditos a los que se refiere la presente sección. Para tal efecto, emplearán</t>
+          <t>Crédito PERSONAL. A los créditos que sean cobrados por la Institución por cualquier medio de pago distinto de la cuenta de nómina.  
+MICROCRÉDITOS. A los créditos otorgados a personas físicas cuyos recursos estén destinados a financiar actividades de producción o comercialización de bienes o prestación de servicios, en los que la fuente principal de pago la constituyen los ingresos obtenidos por dichas actividades y cuyos montos y plazos serán bajo alguna de las modalidades siguientes:</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras</t>
+          <t>A los créditos que sean cobrados por la Institución por cualquier medio de pago distinto de la cuenta de nómina</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -729,7 +732,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>¿Qué enfoques pueden adoptar las instituciones para el cálculo de reservas preventivas y cuáles son sus requisitos?</t>
+          <t>¿Qué se entiendo por saldo a pagar?</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -737,13 +740,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes:  
-I. El Enfoque Estándar, el cual resulta aplicable a todas las carteras consideradas en la definición de Cartera Crediticia contenida en el Artículo 1 de las presentes disposiciones. Las Instituciones que adopten este enfoque para el cálculo de sus reservas preventivas deberán sujetarse a los requisitos y procedimientos contenidos dentro del Capítulo V Bis.</t>
+          <t>I. Insumos y definiciones:  
+| Saldo a Pagar | Importe exigible de la deuda a la fecha de corte en la cual inicia el Periodo de Pago que el acreditado tiene por pagar a la Institución.
+Esta variable deberá estar expresada en moneda nacional y a dos decimales. |
+| --- | --- |
+| Pago Realizado | Suma de los pagos realizados por el acreditado en el Periodo de Pago.
+Esta variable deberá estar expresada en moneda nacional, a dos decimales y su valor deberá ser mayor o igual a cero. |</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes: I. El Enfoque Estándar... II. El Enfoque Interno...</t>
+          <t>Importe exigible de la deuda a la fecha de corte en la cual inicia el Periodo de Pago que el acreditado tiene por pagar a la Institución</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -756,7 +763,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos clasificados como "B" en la Cartera Crediticia de Consumo no Revolvente?</t>
+          <t>¿Cómo se determina la reservas para los créditos en etapa 2?</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -764,15 +771,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>### Artículo 91 Bis 1.- La Probabilidad de Incumplimiento de los créditos clasificados como “B, A, N, P u O” conforme al Artículo 91 Bis de las presentes disposiciones, se determinará de acuerdo con las fracciones I a V siguientes, según corresponda:  
-I. La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente:  
-a) Si $ATR_{i}^{B} &amp;gt; 3$ o cuando el crédito se encuentre en etapa 3:  
-$$</t>
+          <t>Los cálculos requeridos para obtener las reservas para la vida completa de los créditos deberán realizarse considerando cuatro decimales.  
+El monto de reservas para los créditos en etapa 2 será el resultado de:  
+$$
+\ Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)
+$$  
+El monto total de reservas a constituir por la Institución para esta cartera, será igual a la sumatoria de las reservas de cada crédito.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como “B” deberá obtenerse conforme a lo siguiente: a) Si $ATR_{i}^{B} &gt; 3$ o cuando el crédito se encuentre en etapa 3: PI_{i}^{B} = 100%</t>
+          <t>Reservas\ Etapa\ 2_i = \max\left(\text{Reservas\ Vida\ Completa}_i, PI_i^X \times SP_i^X \times EI_i^X\right)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -812,7 +821,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>¿Qué criterios deben seguir las instituciones para migrar un crédito entre etapas de riesgo?</t>
+          <t>¿Se pueden reportar tasas de interés en cero?</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -820,12 +829,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Adicionalmente, si las Instituciones cuentan con algún elemento para determinar que un crédito debe de migrar de etapa 1 a etapa 2, o de etapa 1 a etapa 3, o de etapa 2 a etapa 3, estas podrán realizarlo sin la necesidad del cumplimiento de lo contenido en la tabla anterior. Los criterios bajo los cuales las Instituciones podrán realizar dicha migración deberán estar formalizados dentro de los manuales de políticas y procedimientos de la Institución y deberán ser aplicados de forma consistente.</t>
+          <t>62.- TASA DE INTERÉS ANUAL COBRADA A LA O EL CLIENTE (Conforme al Art. 91 II Bis de la CUB).- Se debe reportar la Tasa de Interés Anual cobrada a la o el cliente, conforme a CUB Art. 91 II Bis.  
+En casos donde la tasa de interés anual sea igual a cero, se deberá utilizar un valor fijo de 0.00001%. El porcentaje expresado en base cien, con cinco decimales, sin redondear y sin el signo de porcentaje (%) ejemplo: 10.05601% se deberá anotar 10.05601.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Los criterios bajo los cuales las Instituciones podrán realizar dicha migración deberán estar formalizados dentro de los manuales de políticas y procedimientos de la Institución y deberán ser aplicados de forma consistente.</t>
+          <t>En casos donde la tasa de interés anual sea igual a cero, se deberá utilizar un valor fijo de 0.00001%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -838,7 +848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>¿Cómo se determina la Probabilidad de Incumplimiento para créditos con ACT_i ≤ 3?</t>
+          <t>¿Cuándo no exista información del acreditado en las sociedades de información crediticia que factor de riesgo se aplica?</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -846,25 +856,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>IV. La Probabilidad de Incumplimiento de los créditos de la Cartera Crediticia de Consumo no Revolvente clasificados como "P", deberá obtenerse conforme a lo siguiente:  
-a) Si $ATR_{i}^{P} &amp;gt; 3$ o cuando el crédito se encuentre etapa 3, entonces:  
-$$
-P I_{i}^{P} = 100\%
-$$  
-b) Si $ATR_{i}^{P} \leq 3$ entonces:  
-$$
-P I_{i}^{P} = \frac{1}{1 + e^{-Z_{i}^{P}}}
-$$  
-En donde:  
-$$
-Z_{i}^{P} = \beta_{0}^{P} + \sum_{j=1}^{8} \beta_{j}^{P} \times Var_{ij}^{P}
-$$  
-| Coeficiente | Valor |</t>
+          <t>Cuando no exista información de la persona acreditada en las sociedades de información crediticia autorizadas, las Instituciones deberán asignar el valor de 13 siempre y cuando no se cuente con evidencia dentro de la Institución de que la persona acreditada cuenta con atrasos en alguno de los créditos con la propia Institución.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PI_i = \frac{1}{1 + e^{-Z_i}}</t>
+          <t>Cuando no exista información del acreditado en las sociedades de información crediticia autorizadas, las Instituciones para realizar el cálculo de las variables...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -877,94 +874,13 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿Cómo pueden las instituciones financieras reducir las reservas preventivas a través del reconocimiento de garantías?</t>
+          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>### Artículo 97 Bis 6.- Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas derivadas de la calificación de cartera de los créditos a los que se refiere la presente sección. Para tal efecto, emplearán</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Las Instituciones podrán reconocer en la estimación de la Severidad de la Pérdida de los créditos las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito, con la finalidad de disminuir las reservas preventivas</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Q17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>¿Qué tipos de garantías son reconocidos para la estimación de la Severidad de la Pérdida de los créditos?</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>| 4 | 7 | La severidad de la pérdida de la persona acreditada no aplica para créditos con garantías paso y medida o primeras perdidas relativas a la persona garante. | 3 |
-| 4 | 8 | La severidad de la pérdida de la persona garante solo aplica para créditos con garantías paso y medida o primeras perdidas relativas a la persona garante. | 3 |
-| 4 | 9 | Cuando el tipo de garantía sea distinto a las garantías reales financieras el campo tipo de garantía real financiera debe ser igual a 0. | 3 |</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>las garantías reales financieras, garantías mobiliarias inscritas en favor de las Instituciones en el registro único de garantías mobiliarias, así como las garantías personales y Seguros de Crédito</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Q18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>¿En qué condiciones deben las instituciones aplicar el apartado E para calcular sus reservas?</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Las Instituciones, podrán optar por alguno de los enfoques siguientes:  
-I. El Enfoque Estándar, el cual resulta aplicable a todas las carteras consideradas en la definición de Cartera Crediticia contenida en el Artículo 1 de las presentes disposiciones. Las Instituciones que adopten este enfoque para el cálculo de sus reservas preventivas deberán sujetarse a los requisitos y procedimientos contenidos dentro del Capítulo V Bis.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>emplearán el presente apartado siempre que calculen sus reservas con la metodología de calificación de cartera a la que se refiere esta sección</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Q19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Cobertura de Liquidez y cómo debe expresarse el resultado porcentual?</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr">
         <is>
           <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.  
 $$
@@ -972,9 +888,88 @@
 $$</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>¿Cómo se determina el flujo de salida contingente por operaciones con instrumentos financieros derivados?</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>La forma de calcular el flujo de salida y de entrada por operaciones con instrumentos financieros derivados será la siguiente:</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Las Instituciones deberán calcular el flujo de salida contingente por operaciones con instrumentos financieros derivados como el máximo valor absoluto de la suma de los montos referidos en los incisos a) y b) siguientes</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>¿Cómo se calcula el flujo total de entrada de efectivo?</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>V. El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el  
+75 por ciento del flujo total de salida de efectivo calculado conforme el artículo 11 de las presentes disposiciones.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el 75 por ciento del flujo total de salida de efectivo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>¿Qué factor de salida se aplica a depósitos en cuentas transaccionales de personas físicas cubiertos por el IPAB?</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>| | I.1.2 Depósitos en Cuentas Transaccionales de personas físicas y de personas físicas con actividad empresarial, elegibles como operaciones pasivas garantizadas por el IPAB de acuerdo a la Ley para la Protección al Ahorro Bancario, cuyo monto excede el límite establecido en esta, o el que corresponda en la jurisdicción en que se hayan constituido las cuentas. | |</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Coeficiente de Cobertura de Liquidez será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
+          <t>I.1.2.1 Monto que no excede el límite establecido en la Ley para la Protección al Ahorro Bancario para las operaciones pasivas garantizadas por el IPAB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -987,7 +982,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>¿Cómo se determina el flujo de salida contingente por operaciones con instrumentos financieros derivados?</t>
+          <t>¿Cómo se registran las operaciones de compra-venta fecha valor para calcular el coeficiente de cobertura de liquidez?</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -995,12 +990,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>La forma de calcular el flujo de salida y de entrada por operaciones con instrumentos financieros derivados será la siguiente:</t>
+          <t>del Coeficiente de Cobertura de Liquidez. Adicionalmente, tanto para las operaciones activas como pasivas en las que la propia Institución o la contraparte tienen el derecho de ejercer el cobro en algún momento dentro del horizonte de 30 días, se asumirá que dicha opción será ejercida cuando dicha operación se encuentre dentro del dinero.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Las Instituciones deberán calcular el flujo de salida contingente por operaciones con instrumentos financieros derivados como el máximo valor absoluto de la suma de los montos referidos en los incisos a) y b) siguientes</t>
+          <t>Compensar para cada operación de compra venta de títulos pactada a una fecha valor, la parte activa y pasiva de la misma operación e incluir el monto resultante como flujo de entrada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1013,92 +1008,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>¿Cómo se calcula el flujo total de entrada de efectivo?</t>
+          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Financiamiento Estable Neto y cómo debe expresarse el resultado porcentual?</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>V. El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el  
-75 por ciento del flujo total de salida de efectivo calculado conforme el artículo 11 de las presentes disposiciones.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>El flujo total de entrada de efectivo será el monto que resulte menor entre: i) la suma de todos los flujos de entrada de efectivo calculados de conformidad con la fracción I anterior, y ii) el 75 por ciento del flujo total de salida de efectivo</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Q22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>¿Qué factor de salida se aplica a depósitos en cuentas transaccionales de personas físicas cubiertos por el IPAB?</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>| | I.1.2 Depósitos en Cuentas Transaccionales de personas físicas y de personas físicas con actividad empresarial, elegibles como operaciones pasivas garantizadas por el IPAB de acuerdo a la Ley para la Protección al Ahorro Bancario, cuyo monto excede el límite establecido en esta, o el que corresponda en la jurisdicción en que se hayan constituido las cuentas. | |</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>I.1.2.1 Monto que no excede el límite establecido en la Ley para la Protección al Ahorro Bancario para las operaciones pasivas garantizadas por el IPAB</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Q23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>¿Cómo se registran las operaciones de compra-venta fecha valor para calcular el coeficiente de cobertura de liquidez?</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>del Coeficiente de Cobertura de Liquidez. Adicionalmente, tanto para las operaciones activas como pasivas en las que la propia Institución o la contraparte tienen el derecho de ejercer el cobro en algún momento dentro del horizonte de 30 días, se asumirá que dicha opción será ejercida cuando dicha operación se encuentre dentro del dinero.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Compensar para cada operación de compra venta de títulos pactada a una fecha valor, la parte activa y pasiva de la misma operación e incluir el monto resultante como flujo de entrada</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Q24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>¿Cuál es la fórmula regulatoria para calcular el Coeficiente de Financiamiento Estable Neto y cómo debe expresarse el resultado porcentual?</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.  
 $$
@@ -1106,55 +1022,55 @@
 $$</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto será el que resulte de aplicar la fórmula siguiente y deberá expresarse como porcentaje redondeado a la centésima de punto porcentual más cercana.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Q25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>¿Con qué periodicidad debe reportarse el CFEN al Banco de México y a qué fecha de cálculo corresponde?</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>### PERIODICIDAD DE LA INFORMACIÓN  
 Deberán proporcionar al Banco de México, la información correspondiente a los meses de febrero, abril, junio, agosto, octubre y diciembre, de cada año. Al efecto, deberán incluir un registro por cada crédito.</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>El Coeficiente de Financiamiento Estable Neto que corresponda al último Día Hábil de cada mes deberá reportarse durante los primeros dieciséis Días Hábiles del mes inmediato siguiente.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Q26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Disponible para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>| Nivel de Coeficiente de Financiamiento Estable Neto (CFEN) | Número de reportes mensuales del CFEN por debajo de 100%, incluyendo el más reciente reporte, durante los últimos 12 meses: | | |
 | --- | --- | --- | --- |
@@ -1163,28 +1079,28 @@
 | Menor a 90 y mayor o igual a 70, es decir: 70 &lt; CFEN &lt; 90 | Escenario III | Escenario IV | |</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Disponible: al monto que resulte de sumar los pasivos y capital señalados en el Anexo 6 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Q27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>¿Qué se entiende por Monto de Financiamiento Estable Requerido para efectos del CFEN?</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>| Nivel de Coeficiente de Financiamiento Estable Neto (CFEN) | Número de reportes mensuales del CFEN por debajo de 100%, incluyendo el más reciente reporte, durante los últimos 12 meses: | | |
 | --- | --- | --- | --- |
@@ -1193,56 +1109,56 @@
 | Menor a 90 y mayor o igual a 70, es decir: 70 &lt; CFEN &lt; 90 | Escenario III | Escenario IV | |</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Monto de Financiamiento Estable Requerido: al monto que resulte de sumar: (i) los activos no restringidos y otras operaciones señaladas en el Anexo 7 de las presentes disposiciones</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Q28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>¿Qué factor de financiamiento estable disponible se asigna al capital fundamental, capital básico no fundamental y pasivos con plazo residual igual o mayor a un año?</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>I. Pasivos y capital con factor del 100%  
 A. Capital fundamental definido en las Disposiciones artículo 2 Bis 6, fracción I, inciso a), sin considerar las deducciones establecidas en dicha fracción y Capital Básico No Fundamental definido en las Disposiciones en el artículo 2 Bis 6, fracción II.
 B. El total de cualquier instrumento de capital no incluido en el concepto anterior que tiene un plazo remanente mayor o igual a un año, excluyendo aquellos instrumentos</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Los factores para la determinación del financiamiento estable disponible serán: I. Pasivos y capital con factor del 100% A. Capital fundamental</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Q29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>¿Cuál es la definición de liquidez intradía según las herramientas de monitoreo del Comité de Basilea?</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Herramientas de monitoreo para la gestión de la liquidez intradía - traducción al español
 Página 1 de 16  
@@ -1250,83 +1166,83 @@
 de Supervisión Bancaria</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Liquidez intradía: fondos a los que se puede acceder durante el día hábil, usualmente para permitir que los bancos realicen pagos en tiempo real;</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Q30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>¿Cuáles son las principales fuentes propias de liquidez intradía que puede utilizar un banco durante el día hábil?</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>### B. Fuentes y uso de la liquidez intradía  
 10. A continuación se presentan los principales elementos que componen las fuentes y el uso de la liquidez intradía de un banco. La lista no debe considerarse exhaustiva.</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>(i) Fuentes Fuentes propias - Saldos de reserva en el banco central; - Colateral pignorado con el banco central o con sistemas auxiliares</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Q31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>¿Cómo se define un escenario de tensión de contraparte?</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Escenarios de tensión  
 (i) Tensión financiera propia: el banco sufre, o se percibe que sufre, un evento de tensión  
 30. Para un participante directo, la tensión financiera y/u operativa propia puede provocar que las contrapartes difieran pagos y/o retiren líneas de crédito intradía. Esto, a su vez, puede ocasionar que el banco tenga que financiar una mayor parte de sus pagos con sus propias fuentes de liquidez intradía para evitar diferir sus propios pagos.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>(ii) Tensión de contraparte: una contraparte importante sufre un evento de tensión intradía que le impide realizar pagos</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Q32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>¿Cómo se calcula el uso máximo diario de liquidez intradía a partir de la posición neta acumulada de pagos enviados y recibidos?</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Figura 1. Uso máximo diario de liquidez intradía  
 Herramientas de monitoreo para la gestión de la liquidez intradía - traducción al español
@@ -1334,39 +1250,39 @@
 La figura ilustra una trayectoria de posición neta acumulada durante el día: el mayor valor positivo corresponde a la posición neta acumulada positiva más alta, mientras que el punto más bajo corresponde a la mayor posición neta acumulada negativa. En el ejemplo, el uso de liquidez intradía equivale a 10 unidades.</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>(i) Uso máximo diario de liquidez intradía 13. Esta herramienta permitirá a los supervisores monitorear el uso de liquidez intradía de un banco en condiciones normales.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Q33</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>¿Qué son las obligaciones con horario específico y por qué su incumplimiento puede generar riesgo financiero o reputacional?</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>## (iv) Obligaciones con horario específico  
 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco. La falta de liquidación oportuna de estas obligaciones podría generar una penalización financiera, daño reputacional para el banco o pérdida de negocio futuro.</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>(iv) Obligaciones con horario específico 22. Esta herramienta permitirá a los supervisores comprender mejor las obligaciones con horario específico de un banco.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
